--- a/owlcms/src/main/resources/templates/protocol/PanAmProtocol-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/protocol/PanAmProtocol-LETTER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms4\owlcms\src\main\resources\templates\protocol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18887C74-9773-400E-B56A-FA2159BCB89E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B0CD8CA-69E4-4B5B-8797-998C82FBD65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6150" yWindow="2520" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="525" yWindow="2475" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -1040,7 +1040,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1286,91 +1286,103 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1848,12 +1860,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Feuil4">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X125"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="1"/>
     <col min="2" max="2" width="5.42578125" style="1" customWidth="1"/>
@@ -1878,7 +1890,7 @@
     <col min="25" max="25" width="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A1" s="32" t="s">
         <v>20</v>
       </c>
@@ -1891,22 +1903,22 @@
       <c r="J1" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="102" t="s">
+      <c r="K1" s="96" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-    </row>
-    <row r="2" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="96"/>
+      <c r="P1" s="96"/>
+      <c r="Q1" s="96"/>
+      <c r="R1" s="96"/>
+      <c r="S1" s="96"/>
+      <c r="T1" s="96"/>
+      <c r="U1" s="96"/>
+      <c r="V1" s="96"/>
+    </row>
+    <row r="2" spans="1:24" ht="19.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A2" s="35" t="s">
         <v>21</v>
       </c>
@@ -1933,7 +1945,7 @@
       <c r="T2" s="40"/>
       <c r="U2" s="40"/>
     </row>
-    <row r="3" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="19.5" customHeight="1" ns3:dyDescent="0.25">
       <c r="A3" s="41" t="s">
         <v>22</v>
       </c>
@@ -1941,13 +1953,13 @@
       <c r="J3" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="101" t="s">
+      <c r="K3" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="L3" s="101"/>
-      <c r="M3" s="101"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="101"/>
+      <c r="L3" s="112"/>
+      <c r="M3" s="112"/>
+      <c r="N3" s="112"/>
+      <c r="O3" s="112"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="43"/>
       <c r="R3" s="23" t="s">
@@ -1960,7 +1972,7 @@
       <c r="U3" s="45"/>
       <c r="V3" s="74"/>
     </row>
-    <row r="4" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="19.5" customHeight="1" ns3:dyDescent="0.25">
       <c r="A4" s="41" t="s">
         <v>24</v>
       </c>
@@ -1971,57 +1983,57 @@
       <c r="J4" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="97" t="s">
+      <c r="K4" s="124" t="s">
         <v>79</v>
       </c>
-      <c r="L4" s="97"/>
-      <c r="M4" s="97"/>
-      <c r="N4" s="97"/>
-      <c r="O4" s="97"/>
-      <c r="P4" s="97"/>
-      <c r="Q4" s="97"/>
-      <c r="R4" s="97"/>
-      <c r="S4" s="97"/>
-      <c r="T4" s="97"/>
-      <c r="U4" s="97"/>
-      <c r="V4" s="97"/>
-    </row>
-    <row r="5" spans="1:24" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="6" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L4" s="124"/>
+      <c r="M4" s="124"/>
+      <c r="N4" s="124"/>
+      <c r="O4" s="124"/>
+      <c r="P4" s="124"/>
+      <c r="Q4" s="124"/>
+      <c r="R4" s="124"/>
+      <c r="S4" s="124"/>
+      <c r="T4" s="124"/>
+      <c r="U4" s="124"/>
+      <c r="V4" s="124"/>
+    </row>
+    <row r="5" spans="1:24" ht="6" customHeight="1" ns3:dyDescent="0.2"/>
+    <row r="6" spans="1:24" ht="15" customHeight="1" ns3:dyDescent="0.2">
       <c r="A6" s="7"/>
       <c r="C6" s="8"/>
       <c r="H6" s="7"/>
       <c r="I6" s="9"/>
       <c r="J6" s="7"/>
-      <c r="K6" s="108" t="s">
+      <c r="K6" s="101" t="s">
         <v>38</v>
       </c>
-      <c r="L6" s="109"/>
-      <c r="M6" s="110"/>
+      <c r="L6" s="102"/>
+      <c r="M6" s="103"/>
       <c r="N6" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="O6" s="108" t="s">
+      <c r="O6" s="101" t="s">
         <v>39</v>
       </c>
-      <c r="P6" s="109"/>
-      <c r="Q6" s="110"/>
+      <c r="P6" s="102"/>
+      <c r="Q6" s="103"/>
       <c r="R6" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="S6" s="106" t="s">
+      <c r="S6" s="99" t="s">
         <v>45</v>
       </c>
-      <c r="T6" s="104" t="s">
+      <c r="T6" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="U6" s="111" t="s">
+      <c r="U6" s="104" t="s">
         <v>80</v>
       </c>
-      <c r="V6" s="112"/>
+      <c r="V6" s="105"/>
       <c r="X6"/>
     </row>
-    <row r="7" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>40</v>
       </c>
@@ -2034,10 +2046,10 @@
       <c r="D7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="108" t="s">
+      <c r="E7" s="101" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="110"/>
+      <c r="F7" s="103"/>
       <c r="G7" s="11" t="s">
         <v>34</v>
       </c>
@@ -2074,12 +2086,12 @@
       <c r="R7" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="S7" s="107"/>
-      <c r="T7" s="105"/>
-      <c r="U7" s="113"/>
-      <c r="V7" s="114"/>
-    </row>
-    <row r="8" spans="1:24" s="22" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S7" s="100"/>
+      <c r="T7" s="98"/>
+      <c r="U7" s="106"/>
+      <c r="V7" s="107"/>
+    </row>
+    <row r="8" spans="1:24" s="22" customFormat="1" ht="7.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A8" s="46"/>
       <c r="B8" s="46"/>
       <c r="C8" s="46"/>
@@ -2092,7 +2104,7 @@
       <c r="J8" s="47"/>
       <c r="K8" s="48"/>
     </row>
-    <row r="9" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" ht="21.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A9" s="49" t="s">
         <v>82</v>
       </c>
@@ -2119,7 +2131,7 @@
       <c r="V9" s="77"/>
       <c r="X9"/>
     </row>
-    <row r="10" spans="1:24" s="22" customFormat="1" ht="21.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" s="22" customFormat="1" ht="21.2" customHeight="1" ns3:dyDescent="0.2">
       <c r="A10" s="81" t="s">
         <v>2</v>
       </c>
@@ -2132,10 +2144,10 @@
       <c r="D10" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="117" t="s">
+      <c r="E10" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="118"/>
+      <c r="F10" s="111"/>
       <c r="G10" s="82" t="s">
         <v>5</v>
       </c>
@@ -2178,12 +2190,12 @@
       <c r="T10" s="90" t="s">
         <v>77</v>
       </c>
-      <c r="U10" s="115" t="s">
+      <c r="U10" s="108" t="s">
         <v>81</v>
       </c>
-      <c r="V10" s="116"/>
-    </row>
-    <row r="11" spans="1:24" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="V10" s="109"/>
+    </row>
+    <row r="11" spans="1:24" ht="24.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="B11"/>
       <c r="G11"/>
       <c r="H11"/>
@@ -2201,13 +2213,13 @@
       <c r="W11"/>
       <c r="X11"/>
     </row>
-    <row r="12" spans="1:24" s="32" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="32" customFormat="1" ht="15" ns3:dyDescent="0.25">
       <c r="A12" s="32" t="s">
         <v>63</v>
       </c>
       <c r="J12" s="33"/>
     </row>
-    <row r="13" spans="1:24" s="32" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="32" customFormat="1" ht="6.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A13" s="53"/>
       <c r="B13" s="53"/>
       <c r="C13" s="53"/>
@@ -2231,7 +2243,7 @@
       <c r="U13" s="59"/>
       <c r="V13" s="59"/>
     </row>
-    <row r="14" spans="1:24" s="71" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" s="71" customFormat="1" ht="12" ns3:dyDescent="0.2">
       <c r="A14" s="62" t="s">
         <v>71</v>
       </c>
@@ -2278,7 +2290,7 @@
       <c r="V14" s="70"/>
       <c r="X14" s="64"/>
     </row>
-    <row r="15" spans="1:24" s="52" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" s="52" customFormat="1" ns3:dyDescent="0.2">
       <c r="A15" s="54" t="s">
         <v>56</v>
       </c>
@@ -2325,98 +2337,103 @@
       <c r="V15" s="56"/>
       <c r="X15" s="56"/>
     </row>
-    <row r="16" spans="1:24" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="98" t="s">
+    <row r="16" spans="1:24" ht="6" customHeight="1" ns3:dyDescent="0.2">
+      <c r="C16" s="123"/>
+      <c r="D16" s="123"/>
+    </row>
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="20.25" customHeight="1" ns3:dyDescent="0.2">
+      <c r="A17" s="113" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="98"/>
-      <c r="C17" s="99" t="s">
+      <c r="B17" s="113"/>
+      <c r="C17" s="117" t="s">
         <v>95</v>
       </c>
-      <c r="D17" s="99"/>
-      <c r="E17" s="98" t="s">
+      <c r="D17" s="117"/>
+      <c r="E17" s="113" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="95"/>
-      <c r="G17" s="71"/>
-      <c r="H17" s="14"/>
-      <c r="J17" s="98" t="s">
+      <c r="F17" s="116"/>
+      <c r="G17" s="118"/>
+      <c r="H17" s="119"/>
+      <c r="I17" s="120"/>
+      <c r="J17" s="113" t="s">
         <v>49</v>
       </c>
-      <c r="K17" s="98"/>
-      <c r="L17" s="99" t="s">
+      <c r="K17" s="113"/>
+      <c r="L17" s="117" t="s">
         <v>96</v>
       </c>
-      <c r="M17" s="99"/>
-      <c r="N17" s="99"/>
-      <c r="O17" s="99"/>
-      <c r="P17" s="99"/>
-      <c r="Q17" s="103" t="s">
+      <c r="M17" s="117"/>
+      <c r="N17" s="117"/>
+      <c r="O17" s="117"/>
+      <c r="P17" s="117"/>
+      <c r="Q17" s="114" t="s">
         <v>92</v>
       </c>
-      <c r="R17" s="103"/>
-      <c r="S17" s="71"/>
-      <c r="T17" s="14"/>
-      <c r="V17" s="96"/>
+      <c r="R17" s="114"/>
+      <c r="S17" s="118"/>
+      <c r="T17" s="119"/>
+      <c r="U17" s="120"/>
+      <c r="V17" s="121"/>
       <c r="W17" s="14"/>
       <c r="X17" s="14" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="98"/>
-      <c r="B18" s="98"/>
-      <c r="C18" s="100"/>
-      <c r="D18" s="100"/>
-      <c r="E18" s="98"/>
+    <row r="18" spans="1:24" ht="16.5" customHeight="1" ns3:dyDescent="0.2">
+      <c r="A18" s="113"/>
+      <c r="B18" s="113"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="113"/>
       <c r="F18" s="26" t="s">
         <v>85</v>
       </c>
       <c r="G18" s="78"/>
-      <c r="H18" s="94"/>
+      <c r="H18" s="115"/>
       <c r="I18" s="16"/>
-      <c r="J18" s="98"/>
-      <c r="K18" s="98"/>
-      <c r="L18" s="100"/>
-      <c r="M18" s="100"/>
-      <c r="N18" s="100"/>
-      <c r="O18" s="100"/>
-      <c r="P18" s="100"/>
-      <c r="Q18" s="103"/>
-      <c r="R18" s="103"/>
+      <c r="J18" s="113"/>
+      <c r="K18" s="113"/>
+      <c r="L18" s="122"/>
+      <c r="M18" s="122"/>
+      <c r="N18" s="122"/>
+      <c r="O18" s="122"/>
+      <c r="P18" s="122"/>
+      <c r="Q18" s="114"/>
+      <c r="R18" s="114"/>
       <c r="S18" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="T18" s="94"/>
+      <c r="T18" s="115"/>
       <c r="U18" s="16"/>
       <c r="V18" s="16"/>
       <c r="W18"/>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:24" ns3:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="91"/>
       <c r="D19" s="1"/>
       <c r="E19" s="92"/>
       <c r="F19" s="14"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="103" t="s">
+      <c r="J19" s="95" t="s">
         <v>52</v>
       </c>
-      <c r="K19" s="103"/>
+      <c r="K19" s="95"/>
       <c r="M19"/>
       <c r="N19" s="1"/>
       <c r="O19" s="12"/>
-      <c r="Q19" s="103" t="s">
+      <c r="Q19" s="95" t="s">
         <v>84</v>
       </c>
-      <c r="R19" s="103"/>
+      <c r="R19" s="95"/>
       <c r="S19" s="1"/>
       <c r="T19"/>
       <c r="V19" s="12"/>
       <c r="X19"/>
     </row>
-    <row r="20" spans="1:24" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24" ht="13.7" customHeight="1" ns3:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="25" t="s">
         <v>50</v>
@@ -2434,8 +2451,8 @@
       <c r="G20" s="78"/>
       <c r="H20" s="78"/>
       <c r="I20" s="78"/>
-      <c r="J20" s="103"/>
-      <c r="K20" s="103"/>
+      <c r="J20" s="95"/>
+      <c r="K20" s="95"/>
       <c r="L20" s="26" t="s">
         <v>88</v>
       </c>
@@ -2443,8 +2460,8 @@
       <c r="N20" s="78"/>
       <c r="O20" s="78"/>
       <c r="P20" s="78"/>
-      <c r="Q20" s="103"/>
-      <c r="R20" s="103"/>
+      <c r="Q20" s="95"/>
+      <c r="R20" s="95"/>
       <c r="S20" s="26" t="s">
         <v>89</v>
       </c>
@@ -2453,7 +2470,7 @@
       <c r="V20" s="78"/>
       <c r="X20"/>
     </row>
-    <row r="21" spans="1:24" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:24" s="18" customFormat="1" ht="12.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A21" s="19"/>
       <c r="B21" s="24"/>
       <c r="E21" s="17"/>
@@ -2463,11 +2480,11 @@
       <c r="Q21" s="19"/>
       <c r="V21" s="75"/>
     </row>
-    <row r="22" spans="1:24" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="98" t="s">
+    <row r="22" spans="1:24" ht="17.45" customHeight="1" ns3:dyDescent="0.2">
+      <c r="A22" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="B22" s="98"/>
+      <c r="B22" s="94"/>
       <c r="D22" s="1"/>
       <c r="E22" s="92"/>
       <c r="F22" s="14"/>
@@ -2477,19 +2494,19 @@
       <c r="M22"/>
       <c r="N22" s="1"/>
       <c r="O22" s="12"/>
-      <c r="Q22" s="98" t="s">
+      <c r="Q22" s="94" t="s">
         <v>83</v>
       </c>
-      <c r="R22" s="98"/>
+      <c r="R22" s="94"/>
       <c r="S22" s="1"/>
       <c r="T22"/>
       <c r="V22" s="12"/>
       <c r="W22"/>
       <c r="X22"/>
     </row>
-    <row r="23" spans="1:24" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="98"/>
-      <c r="B23" s="98"/>
+    <row r="23" spans="1:24" ht="13.7" customHeight="1" ns3:dyDescent="0.2">
+      <c r="A23" s="94"/>
+      <c r="B23" s="94"/>
       <c r="C23" s="26" t="s">
         <v>90</v>
       </c>
@@ -2509,8 +2526,8 @@
       <c r="M23" s="78"/>
       <c r="N23" s="78"/>
       <c r="O23" s="78"/>
-      <c r="Q23" s="98"/>
-      <c r="R23" s="98"/>
+      <c r="Q23" s="94"/>
+      <c r="R23" s="94"/>
       <c r="S23" s="26" t="s">
         <v>91</v>
       </c>
@@ -2520,7 +2537,7 @@
       <c r="W23"/>
       <c r="X23"/>
     </row>
-    <row r="24" spans="1:24" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:24" s="18" customFormat="1" ht="11.25" ns3:dyDescent="0.2">
       <c r="B24" s="19"/>
       <c r="F24" s="15"/>
       <c r="G24" s="93"/>
@@ -2533,7 +2550,7 @@
       <c r="S24" s="19"/>
       <c r="V24" s="75"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24" ns3:dyDescent="0.2">
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="H25" s="2"/>
@@ -2545,319 +2562,324 @@
       <c r="S25" s="1"/>
       <c r="T25" s="12"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:24" ns3:dyDescent="0.2">
       <c r="F26" s="1"/>
       <c r="U26" s="12"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:24" ns3:dyDescent="0.2">
       <c r="F27" s="1"/>
       <c r="U27" s="12"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:24" ns3:dyDescent="0.2">
       <c r="F28" s="1"/>
       <c r="U28" s="12"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24" ns3:dyDescent="0.2">
       <c r="F29" s="1"/>
       <c r="U29" s="12"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24" ns3:dyDescent="0.2">
       <c r="F30" s="1"/>
       <c r="U30" s="12"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:24" ns3:dyDescent="0.2">
       <c r="D31" s="20"/>
       <c r="E31" s="20"/>
       <c r="F31" s="1"/>
       <c r="U31" s="12"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:24" ns3:dyDescent="0.2">
       <c r="F32" s="1"/>
       <c r="U32" s="12"/>
     </row>
-    <row r="33" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="6:21" ns3:dyDescent="0.2">
       <c r="F33" s="1"/>
       <c r="U33" s="12"/>
     </row>
-    <row r="34" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="6:21" ns3:dyDescent="0.2">
       <c r="F34" s="1"/>
     </row>
-    <row r="35" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="35" spans="6:21" ns3:dyDescent="0.2">
       <c r="F35" s="1"/>
     </row>
-    <row r="36" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="36" spans="6:21" ns3:dyDescent="0.2">
       <c r="F36" s="1"/>
     </row>
-    <row r="37" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="6:21" ns3:dyDescent="0.2">
       <c r="F37" s="1"/>
     </row>
-    <row r="38" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="6:21" ns3:dyDescent="0.2">
       <c r="F38" s="1"/>
     </row>
-    <row r="39" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="6:21" ns3:dyDescent="0.2">
       <c r="F39" s="1"/>
     </row>
-    <row r="40" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="40" spans="6:21" ns3:dyDescent="0.2">
       <c r="F40" s="1"/>
     </row>
-    <row r="41" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="41" spans="6:21" ns3:dyDescent="0.2">
       <c r="F41" s="1"/>
     </row>
-    <row r="42" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="6:21" ns3:dyDescent="0.2">
       <c r="F42" s="1"/>
     </row>
-    <row r="43" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="43" spans="6:21" ns3:dyDescent="0.2">
       <c r="F43" s="1"/>
     </row>
-    <row r="44" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="6:21" ns3:dyDescent="0.2">
       <c r="F44" s="1"/>
     </row>
-    <row r="45" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="45" spans="6:21" ns3:dyDescent="0.2">
       <c r="F45" s="1"/>
     </row>
-    <row r="46" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="6:21" ns3:dyDescent="0.2">
       <c r="F46" s="1"/>
     </row>
-    <row r="47" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="6:21" ns3:dyDescent="0.2">
       <c r="F47" s="1"/>
     </row>
-    <row r="48" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="6:21" ns3:dyDescent="0.2">
       <c r="F48" s="1"/>
     </row>
-    <row r="49" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="6:6" ns3:dyDescent="0.2">
       <c r="F49" s="1"/>
     </row>
-    <row r="50" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="6:6" ns3:dyDescent="0.2">
       <c r="F50" s="1"/>
     </row>
-    <row r="51" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="6:6" ns3:dyDescent="0.2">
       <c r="F51" s="1"/>
     </row>
-    <row r="52" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="6:6" ns3:dyDescent="0.2">
       <c r="F52" s="1"/>
     </row>
-    <row r="53" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="6:6" ns3:dyDescent="0.2">
       <c r="F53" s="1"/>
     </row>
-    <row r="54" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="6:6" ns3:dyDescent="0.2">
       <c r="F54" s="1"/>
     </row>
-    <row r="55" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="6:6" ns3:dyDescent="0.2">
       <c r="F55" s="1"/>
     </row>
-    <row r="56" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="6:6" ns3:dyDescent="0.2">
       <c r="F56" s="1"/>
     </row>
-    <row r="57" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="6:6" ns3:dyDescent="0.2">
       <c r="F57" s="1"/>
     </row>
-    <row r="58" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="6:6" ns3:dyDescent="0.2">
       <c r="F58" s="1"/>
     </row>
-    <row r="59" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="6:6" ns3:dyDescent="0.2">
       <c r="F59" s="1"/>
     </row>
-    <row r="60" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="6:6" ns3:dyDescent="0.2">
       <c r="F60" s="1"/>
     </row>
-    <row r="61" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="6:6" ns3:dyDescent="0.2">
       <c r="F61" s="1"/>
     </row>
-    <row r="62" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="6:6" ns3:dyDescent="0.2">
       <c r="F62" s="1"/>
     </row>
-    <row r="63" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="6:6" ns3:dyDescent="0.2">
       <c r="F63" s="1"/>
     </row>
-    <row r="64" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="6:6" ns3:dyDescent="0.2">
       <c r="F64" s="1"/>
     </row>
-    <row r="65" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="6:6" ns3:dyDescent="0.2">
       <c r="F65" s="1"/>
     </row>
-    <row r="66" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="6:6" ns3:dyDescent="0.2">
       <c r="F66" s="1"/>
     </row>
-    <row r="67" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="6:6" ns3:dyDescent="0.2">
       <c r="F67" s="1"/>
     </row>
-    <row r="68" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="6:6" ns3:dyDescent="0.2">
       <c r="F68" s="1"/>
     </row>
-    <row r="69" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="6:6" ns3:dyDescent="0.2">
       <c r="F69" s="1"/>
     </row>
-    <row r="70" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="6:6" ns3:dyDescent="0.2">
       <c r="F70" s="1"/>
     </row>
-    <row r="71" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="6:6" ns3:dyDescent="0.2">
       <c r="F71" s="1"/>
     </row>
-    <row r="72" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="6:6" ns3:dyDescent="0.2">
       <c r="F72" s="1"/>
     </row>
-    <row r="73" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="6:6" ns3:dyDescent="0.2">
       <c r="F73" s="1"/>
     </row>
-    <row r="74" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="6:6" ns3:dyDescent="0.2">
       <c r="F74" s="1"/>
     </row>
-    <row r="75" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="6:6" ns3:dyDescent="0.2">
       <c r="F75" s="1"/>
     </row>
-    <row r="76" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="6:6" ns3:dyDescent="0.2">
       <c r="F76" s="1"/>
     </row>
-    <row r="77" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="6:6" ns3:dyDescent="0.2">
       <c r="F77" s="1"/>
     </row>
-    <row r="78" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="6:6" ns3:dyDescent="0.2">
       <c r="F78" s="1"/>
     </row>
-    <row r="79" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="6:6" ns3:dyDescent="0.2">
       <c r="F79" s="1"/>
     </row>
-    <row r="80" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="6:6" ns3:dyDescent="0.2">
       <c r="F80" s="1"/>
     </row>
-    <row r="81" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="6:6" ns3:dyDescent="0.2">
       <c r="F81" s="1"/>
     </row>
-    <row r="82" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="6:6" ns3:dyDescent="0.2">
       <c r="F82" s="1"/>
     </row>
-    <row r="83" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="6:6" ns3:dyDescent="0.2">
       <c r="F83" s="1"/>
     </row>
-    <row r="84" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="6:6" ns3:dyDescent="0.2">
       <c r="F84" s="1"/>
     </row>
-    <row r="85" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="6:6" ns3:dyDescent="0.2">
       <c r="F85" s="1"/>
     </row>
-    <row r="86" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="6:6" ns3:dyDescent="0.2">
       <c r="F86" s="1"/>
     </row>
-    <row r="87" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="6:6" ns3:dyDescent="0.2">
       <c r="F87" s="1"/>
     </row>
-    <row r="88" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="6:6" ns3:dyDescent="0.2">
       <c r="F88" s="1"/>
     </row>
-    <row r="89" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="6:6" ns3:dyDescent="0.2">
       <c r="F89" s="1"/>
     </row>
-    <row r="90" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="6:6" ns3:dyDescent="0.2">
       <c r="F90" s="1"/>
     </row>
-    <row r="91" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="6:6" ns3:dyDescent="0.2">
       <c r="F91" s="1"/>
     </row>
-    <row r="92" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="6:6" ns3:dyDescent="0.2">
       <c r="F92" s="1"/>
     </row>
-    <row r="93" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="6:6" ns3:dyDescent="0.2">
       <c r="F93" s="1"/>
     </row>
-    <row r="94" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="6:6" ns3:dyDescent="0.2">
       <c r="F94" s="1"/>
     </row>
-    <row r="95" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="6:6" ns3:dyDescent="0.2">
       <c r="F95" s="1"/>
     </row>
-    <row r="96" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="6:6" ns3:dyDescent="0.2">
       <c r="F96" s="1"/>
     </row>
-    <row r="97" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="6:6" ns3:dyDescent="0.2">
       <c r="F97" s="1"/>
     </row>
-    <row r="98" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="6:6" ns3:dyDescent="0.2">
       <c r="F98" s="1"/>
     </row>
-    <row r="99" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="6:6" ns3:dyDescent="0.2">
       <c r="F99" s="1"/>
     </row>
-    <row r="100" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="6:6" ns3:dyDescent="0.2">
       <c r="F100" s="1"/>
     </row>
-    <row r="101" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="6:6" ns3:dyDescent="0.2">
       <c r="F101" s="1"/>
     </row>
-    <row r="102" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="6:6" ns3:dyDescent="0.2">
       <c r="F102" s="1"/>
     </row>
-    <row r="103" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="6:6" ns3:dyDescent="0.2">
       <c r="F103" s="1"/>
     </row>
-    <row r="104" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="6:6" ns3:dyDescent="0.2">
       <c r="F104" s="1"/>
     </row>
-    <row r="105" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="6:6" ns3:dyDescent="0.2">
       <c r="F105" s="1"/>
     </row>
-    <row r="106" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="6:6" ns3:dyDescent="0.2">
       <c r="F106" s="1"/>
     </row>
-    <row r="107" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="6:6" ns3:dyDescent="0.2">
       <c r="F107" s="1"/>
     </row>
-    <row r="108" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="6:6" ns3:dyDescent="0.2">
       <c r="F108" s="1"/>
     </row>
-    <row r="109" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="6:6" ns3:dyDescent="0.2">
       <c r="F109" s="1"/>
     </row>
-    <row r="110" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="6:6" ns3:dyDescent="0.2">
       <c r="F110" s="1"/>
     </row>
-    <row r="111" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="6:6" ns3:dyDescent="0.2">
       <c r="F111" s="1"/>
     </row>
-    <row r="112" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="6:6" ns3:dyDescent="0.2">
       <c r="F112" s="1"/>
     </row>
-    <row r="113" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="6:6" ns3:dyDescent="0.2">
       <c r="F113" s="1"/>
     </row>
-    <row r="114" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="6:6" ns3:dyDescent="0.2">
       <c r="F114" s="1"/>
     </row>
-    <row r="115" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="6:6" ns3:dyDescent="0.2">
       <c r="F115" s="1"/>
     </row>
-    <row r="116" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="6:6" ns3:dyDescent="0.2">
       <c r="F116" s="1"/>
     </row>
-    <row r="117" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="6:6" ns3:dyDescent="0.2">
       <c r="F117" s="1"/>
     </row>
-    <row r="118" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="6:6" ns3:dyDescent="0.2">
       <c r="F118" s="1"/>
     </row>
-    <row r="119" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="6:6" ns3:dyDescent="0.2">
       <c r="F119" s="1"/>
     </row>
-    <row r="120" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="6:6" ns3:dyDescent="0.2">
       <c r="F120" s="1"/>
     </row>
-    <row r="121" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="6:6" ns3:dyDescent="0.2">
       <c r="F121" s="1"/>
     </row>
-    <row r="122" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="6:6" ns3:dyDescent="0.2">
       <c r="F122" s="1"/>
     </row>
-    <row r="123" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="6:6" ns3:dyDescent="0.2">
       <c r="F123" s="1"/>
     </row>
-    <row r="124" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="6:6" ns3:dyDescent="0.2">
       <c r="F124" s="1"/>
     </row>
-    <row r="125" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="6:6" ns3:dyDescent="0.2">
       <c r="F125" s="1"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="21">
+    <mergeCell ref="K4:V4"/>
+    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="L17:P18"/>
     <mergeCell ref="K3:O3"/>
     <mergeCell ref="J17:K18"/>
     <mergeCell ref="A22:B23"/>
@@ -2874,11 +2896,6 @@
     <mergeCell ref="Q22:R23"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E10:F10"/>
-    <mergeCell ref="K4:V4"/>
-    <mergeCell ref="A17:B18"/>
-    <mergeCell ref="C17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="L17:P18"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:D8">
     <cfRule type="expression" dxfId="2" priority="7" stopIfTrue="1">
@@ -2896,24 +2913,24 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation showErrorMessage="1" sqref="K4 F23 C20 S18 S23 F20 C23 L20 S20 C17 L17 F18" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="H10" xr:uid="{00000000-0002-0000-0000-000001000000}"/>
-    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="H11:H13" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation showErrorMessage="1" sqref="K4 F23 C20 S18 S23 F20 C23 L20 S20 C17 L17 F18" ns2:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="H10" ns2:uid="{00000000-0002-0000-0000-000001000000}"/>
+    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="H11:H13" ns2:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I8" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I8" ns2:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" display="www.federation.org" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="A4" r:id="rId2" display="records@federation.org" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A3" ns4:id="rId1" display="www.federation.org" ns2:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A4" ns4:id="rId2" display="records@federation.org" ns2:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.31496062992125984" right="0.35433070866141736" top="0.39370078740157483" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="70" firstPageNumber="0" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
+  <pageSetup paperSize="1" scale="70" firstPageNumber="0" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" ns4:id="rId3"/>
   <headerFooter alignWithMargins="0"/>
-  <legacyDrawing r:id="rId4"/>
+  <legacyDrawing ns4:id="rId4"/>
 </worksheet>
 </file>
--- a/owlcms/src/main/resources/templates/protocol/PanAmProtocol-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/protocol/PanAmProtocol-LETTER.xlsx
@@ -1860,7 +1860,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Feuil4">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/owlcms/src/main/resources/templates/protocol/PanAmProtocol-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/protocol/PanAmProtocol-LETTER.xlsx
@@ -124,7 +124,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>jx:if(condition="group.records.size() &gt; 0"  lastCell="V15")</t>
+          <t>jx:if(condition="session.records.size() &gt; 0"  lastCell="V15")</t>
         </r>
       </text>
     </comment>
@@ -137,7 +137,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>jx:each(items="group.records" var="r" lastCell="V15")</t>
+          <t>jx:each(items="session.records" var="r" lastCell="V15")</t>
         </r>
       </text>
     </comment>
@@ -444,7 +444,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" ns1:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0;;"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0_)\ _$_ ;_ * \(#,##0&quot;) &quot;_$_ ;_ * \-??_)\ _$_ ;_ @_ "/>
@@ -453,7 +453,7 @@
     <numFmt numFmtId="168" formatCode="0.000;;\-"/>
     <numFmt numFmtId="169" formatCode="0;\-;\-"/>
   </numFmts>
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="112" ns2:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -648,6 +648,505 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
     </font>
   </fonts>
   <fills count="14">
@@ -729,7 +1228,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="102">
     <border>
       <left/>
       <right/>
@@ -1017,6 +1516,576 @@
         <color indexed="64"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
     </border>
   </borders>
   <cellStyleXfs count="19">
@@ -1040,7 +2109,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="212">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1384,6 +2453,283 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="24" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="25" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="26" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="27" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="28" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="29" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="30" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="31" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="32" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="33" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="34" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="35" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="39" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="40" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="41" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="42" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="43" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="44" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="45" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="46" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="47" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="56" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1" applyAlignment="1">
+      <protection locked="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="57" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1" applyAlignment="1">
+      <protection locked="0"/>
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="58" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1" applyAlignment="1">
+      <protection locked="0"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="62" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="63" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="64" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="60" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="61" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="62" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="63" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="64" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="65" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="66" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="67" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="68" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="69" xfId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="70" xfId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="71" xfId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="72" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="73" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="74" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="77" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="78" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="79" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="80" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="81" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="82" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="83" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="84" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="85" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="98" fillId="0" borderId="90" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="99" fillId="0" borderId="91" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="100" fillId="0" borderId="92" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="93" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="94" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="95" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="96" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="97" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="98" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="99" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="100" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="101" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyBorder="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="0" applyProtection="1" applyAlignment="1">
+      <protection locked="0"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyBorder="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1" applyBorder="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyBorder="0" applyFont="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyBorder="0" applyFont="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="19">
@@ -1393,18 +2739,18 @@
     <cellStyle name="Accent4" xfId="4" builtinId="41" customBuiltin="1"/>
     <cellStyle name="Accent5" xfId="5" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Accent6" xfId="6" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Emphase 1" xfId="7" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Emphase 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Emphase 3" xfId="9" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Emphase 1" xfId="7" ns3:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Emphase 2" xfId="8" ns3:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Emphase 3" xfId="9" ns3:uid="{00000000-0005-0000-0000-000008000000}"/>
     <cellStyle name="Hyperlink" xfId="10" builtinId="8"/>
-    <cellStyle name="Lien hypertexte 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Lien hypertexte 2" xfId="11" ns3:uid="{00000000-0005-0000-0000-00000A000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="Normal 3" xfId="13" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="Titre 1" xfId="14" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="Titre 1 1" xfId="15" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="Titre 1 1 1" xfId="16" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="Titre de la feuille" xfId="17" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Normal 2" xfId="12" ns3:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Normal 3" xfId="13" ns3:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Titre 1" xfId="14" ns3:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Titre 1 1" xfId="15" ns3:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Titre 1 1 1" xfId="16" ns3:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Titre de la feuille" xfId="17" ns3:uid="{00000000-0005-0000-0000-000011000000}"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="3">
@@ -1503,11 +2849,11 @@
     </indexedColors>
   </colors>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns4:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns5:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1860,12 +3206,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Feuil4">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X125"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" ns3:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" ns2:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="1"/>
     <col min="2" max="2" width="5.42578125" style="1" customWidth="1"/>
@@ -1890,116 +3236,71 @@
     <col min="25" max="25" width="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="15"/>
-      <c r="J1" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="96" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="96"/>
-      <c r="P1" s="96"/>
-      <c r="Q1" s="96"/>
-      <c r="R1" s="96"/>
-      <c r="S1" s="96"/>
-      <c r="T1" s="96"/>
-      <c r="U1" s="96"/>
-      <c r="V1" s="96"/>
-    </row>
-    <row r="2" spans="1:24" ht="19.5" customHeight="1" ns3:dyDescent="0.2">
-      <c r="A2" s="35" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="4"/>
-      <c r="J2" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" s="76"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="34"/>
-      <c r="O2" s="34"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="S2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T2" s="40"/>
-      <c r="U2" s="40"/>
-    </row>
-    <row r="3" spans="1:24" ht="19.5" customHeight="1" ns3:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="42"/>
-      <c r="J3" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" s="112" t="s">
-        <v>55</v>
-      </c>
-      <c r="L3" s="112"/>
-      <c r="M3" s="112"/>
-      <c r="N3" s="112"/>
-      <c r="O3" s="112"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="S3" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="T3" s="45"/>
-      <c r="U3" s="45"/>
-      <c r="V3" s="74"/>
-    </row>
-    <row r="4" spans="1:24" ht="19.5" customHeight="1" ns3:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="J4" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="K4" s="124" t="s">
-        <v>79</v>
-      </c>
-      <c r="L4" s="124"/>
-      <c r="M4" s="124"/>
-      <c r="N4" s="124"/>
-      <c r="O4" s="124"/>
-      <c r="P4" s="124"/>
-      <c r="Q4" s="124"/>
-      <c r="R4" s="124"/>
-      <c r="S4" s="124"/>
-      <c r="T4" s="124"/>
-      <c r="U4" s="124"/>
-      <c r="V4" s="124"/>
-    </row>
-    <row r="5" spans="1:24" ht="6" customHeight="1" ns3:dyDescent="0.2"/>
-    <row r="6" spans="1:24" ht="15" customHeight="1" ns3:dyDescent="0.2">
+    <row r="1" spans="1:24" ht="24" customHeight="1" ns2:dyDescent="0.25">
+      <c r="A1" s="204" t="inlineStr">
+        <is>
+          <t>${competition.competitionName}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:24" ht="24" customHeight="1" ns2:dyDescent="0.2">
+      <c r="A2" s="203" t="inlineStr">
+        <is>
+          <t>${t.get("Competition.competitionSite")} :</t>
+        </is>
+      </c>
+      <c r="D2" s="205" t="inlineStr">
+        <is>
+          <t>${competition.competitionSite}</t>
+        </is>
+      </c>
+      <c r="K2" s="203" t="inlineStr">
+        <is>
+          <t>${t.get("Competition.competitionCity")} :</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr" s="206">
+        <is>
+          <t>${competition.competitionCity}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:24" ht="24" customHeight="1" ns2:dyDescent="0.25">
+      <c r="A3" s="203" t="inlineStr">
+        <is>
+          <t>${t.get("Competition.competitionDate")} :</t>
+        </is>
+      </c>
+      <c r="D3" s="207" t="inlineStr">
+        <is>
+          <t>${competition.localizedCompetitionDate}</t>
+        </is>
+      </c>
+      <c r="K3" s="210" t="inlineStr">
+        <is>
+          <t>${t.get("Competition.competitionOrganizer")} :</t>
+        </is>
+      </c>
+      <c r="N3" s="208" t="inlineStr">
+        <is>
+          <t>${competition.competitionOrganizer}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="24" customHeight="1" ns2:dyDescent="0.25">
+      <c r="A4" s="211" t="inlineStr">
+        <is>
+          <t>${session != null ? t.get("Group") + " :" : ""}</t>
+        </is>
+      </c>
+      <c r="D4" s="209" t="inlineStr">
+        <is>
+          <t>${session != null ? session.name : ""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="6" customHeight="1" ns2:dyDescent="0.2"/>
+    <row r="6" spans="1:24" ht="15" customHeight="1" ns2:dyDescent="0.2">
       <c r="A6" s="7"/>
       <c r="C6" s="8"/>
       <c r="H6" s="7"/>
@@ -2033,7 +3334,7 @@
       <c r="V6" s="105"/>
       <c r="X6"/>
     </row>
-    <row r="7" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.2">
+    <row r="7" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" ns2:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>40</v>
       </c>
@@ -2091,7 +3392,7 @@
       <c r="U7" s="106"/>
       <c r="V7" s="107"/>
     </row>
-    <row r="8" spans="1:24" s="22" customFormat="1" ht="7.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="8" spans="1:24" s="22" customFormat="1" ht="7.5" customHeight="1" ns2:dyDescent="0.2">
       <c r="A8" s="46"/>
       <c r="B8" s="46"/>
       <c r="C8" s="46"/>
@@ -2104,7 +3405,7 @@
       <c r="J8" s="47"/>
       <c r="K8" s="48"/>
     </row>
-    <row r="9" spans="1:24" ht="21.75" customHeight="1" ns3:dyDescent="0.2">
+    <row r="9" spans="1:24" ht="21.75" customHeight="1" ns2:dyDescent="0.2">
       <c r="A9" s="49" t="s">
         <v>82</v>
       </c>
@@ -2131,7 +3432,7 @@
       <c r="V9" s="77"/>
       <c r="X9"/>
     </row>
-    <row r="10" spans="1:24" s="22" customFormat="1" ht="21.2" customHeight="1" ns3:dyDescent="0.2">
+    <row r="10" spans="1:24" s="22" customFormat="1" ht="21.2" customHeight="1" ns2:dyDescent="0.2">
       <c r="A10" s="81" t="s">
         <v>2</v>
       </c>
@@ -2195,7 +3496,7 @@
       </c>
       <c r="V10" s="109"/>
     </row>
-    <row r="11" spans="1:24" ht="24.75" customHeight="1" ns3:dyDescent="0.2">
+    <row r="11" spans="1:24" ht="24.75" customHeight="1" ns2:dyDescent="0.2">
       <c r="B11"/>
       <c r="G11"/>
       <c r="H11"/>
@@ -2213,13 +3514,13 @@
       <c r="W11"/>
       <c r="X11"/>
     </row>
-    <row r="12" spans="1:24" s="32" customFormat="1" ht="15" ns3:dyDescent="0.25">
+    <row r="12" spans="1:24" s="32" customFormat="1" ht="15" ns2:dyDescent="0.25">
       <c r="A12" s="32" t="s">
         <v>63</v>
       </c>
       <c r="J12" s="33"/>
     </row>
-    <row r="13" spans="1:24" s="32" customFormat="1" ht="6.75" customHeight="1" ns3:dyDescent="0.25">
+    <row r="13" spans="1:24" s="32" customFormat="1" ht="6.75" customHeight="1" ns2:dyDescent="0.25">
       <c r="A13" s="53"/>
       <c r="B13" s="53"/>
       <c r="C13" s="53"/>
@@ -2243,7 +3544,7 @@
       <c r="U13" s="59"/>
       <c r="V13" s="59"/>
     </row>
-    <row r="14" spans="1:24" s="71" customFormat="1" ht="12" ns3:dyDescent="0.2">
+    <row r="14" spans="1:24" s="71" customFormat="1" ht="12" ns2:dyDescent="0.2">
       <c r="A14" s="62" t="s">
         <v>71</v>
       </c>
@@ -2290,7 +3591,7 @@
       <c r="V14" s="70"/>
       <c r="X14" s="64"/>
     </row>
-    <row r="15" spans="1:24" s="52" customFormat="1" ns3:dyDescent="0.2">
+    <row r="15" spans="1:24" s="52" customFormat="1" ns2:dyDescent="0.2">
       <c r="A15" s="54" t="s">
         <v>56</v>
       </c>
@@ -2337,11 +3638,11 @@
       <c r="V15" s="56"/>
       <c r="X15" s="56"/>
     </row>
-    <row r="16" spans="1:24" ht="6" customHeight="1" ns3:dyDescent="0.2">
+    <row r="16" spans="1:24" ht="6" customHeight="1" ns2:dyDescent="0.2">
       <c r="C16" s="123"/>
       <c r="D16" s="123"/>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="20.25" customHeight="1" ns3:dyDescent="0.2">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="20.25" customHeight="1" ns2:dyDescent="0.2">
       <c r="A17" s="113" t="s">
         <v>47</v>
       </c>
@@ -2381,7 +3682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="16.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="18" spans="1:24" ht="16.5" customHeight="1" ns2:dyDescent="0.2">
       <c r="A18" s="113"/>
       <c r="B18" s="113"/>
       <c r="C18" s="122"/>
@@ -2410,7 +3711,7 @@
       <c r="V18" s="16"/>
       <c r="W18"/>
     </row>
-    <row r="19" spans="1:24" ns3:dyDescent="0.2">
+    <row r="19" spans="1:24" ns2:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="91"/>
       <c r="D19" s="1"/>
@@ -2433,7 +3734,7 @@
       <c r="V19" s="12"/>
       <c r="X19"/>
     </row>
-    <row r="20" spans="1:24" ht="13.7" customHeight="1" ns3:dyDescent="0.2">
+    <row r="20" spans="1:24" ht="13.7" customHeight="1" ns2:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="25" t="s">
         <v>50</v>
@@ -2470,7 +3771,7 @@
       <c r="V20" s="78"/>
       <c r="X20"/>
     </row>
-    <row r="21" spans="1:24" s="18" customFormat="1" ht="12.75" customHeight="1" ns3:dyDescent="0.2">
+    <row r="21" spans="1:24" s="18" customFormat="1" ht="12.75" customHeight="1" ns2:dyDescent="0.2">
       <c r="A21" s="19"/>
       <c r="B21" s="24"/>
       <c r="E21" s="17"/>
@@ -2480,7 +3781,7 @@
       <c r="Q21" s="19"/>
       <c r="V21" s="75"/>
     </row>
-    <row r="22" spans="1:24" ht="17.45" customHeight="1" ns3:dyDescent="0.2">
+    <row r="22" spans="1:24" ht="17.45" customHeight="1" ns2:dyDescent="0.2">
       <c r="A22" s="94" t="s">
         <v>69</v>
       </c>
@@ -2504,7 +3805,7 @@
       <c r="W22"/>
       <c r="X22"/>
     </row>
-    <row r="23" spans="1:24" ht="13.7" customHeight="1" ns3:dyDescent="0.2">
+    <row r="23" spans="1:24" ht="13.7" customHeight="1" ns2:dyDescent="0.2">
       <c r="A23" s="94"/>
       <c r="B23" s="94"/>
       <c r="C23" s="26" t="s">
@@ -2537,7 +3838,7 @@
       <c r="W23"/>
       <c r="X23"/>
     </row>
-    <row r="24" spans="1:24" s="18" customFormat="1" ht="11.25" ns3:dyDescent="0.2">
+    <row r="24" spans="1:24" s="18" customFormat="1" ht="11.25" ns2:dyDescent="0.2">
       <c r="B24" s="19"/>
       <c r="F24" s="15"/>
       <c r="G24" s="93"/>
@@ -2550,7 +3851,7 @@
       <c r="S24" s="19"/>
       <c r="V24" s="75"/>
     </row>
-    <row r="25" spans="1:24" ns3:dyDescent="0.2">
+    <row r="25" spans="1:24" ns2:dyDescent="0.2">
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="H25" s="2"/>
@@ -2562,328 +3863,325 @@
       <c r="S25" s="1"/>
       <c r="T25" s="12"/>
     </row>
-    <row r="26" spans="1:24" ns3:dyDescent="0.2">
+    <row r="26" spans="1:24" ns2:dyDescent="0.2">
       <c r="F26" s="1"/>
       <c r="U26" s="12"/>
     </row>
-    <row r="27" spans="1:24" ns3:dyDescent="0.2">
+    <row r="27" spans="1:24" ns2:dyDescent="0.2">
       <c r="F27" s="1"/>
       <c r="U27" s="12"/>
     </row>
-    <row r="28" spans="1:24" ns3:dyDescent="0.2">
+    <row r="28" spans="1:24" ns2:dyDescent="0.2">
       <c r="F28" s="1"/>
       <c r="U28" s="12"/>
     </row>
-    <row r="29" spans="1:24" ns3:dyDescent="0.2">
+    <row r="29" spans="1:24" ns2:dyDescent="0.2">
       <c r="F29" s="1"/>
       <c r="U29" s="12"/>
     </row>
-    <row r="30" spans="1:24" ns3:dyDescent="0.2">
+    <row r="30" spans="1:24" ns2:dyDescent="0.2">
       <c r="F30" s="1"/>
       <c r="U30" s="12"/>
     </row>
-    <row r="31" spans="1:24" ns3:dyDescent="0.2">
+    <row r="31" spans="1:24" ns2:dyDescent="0.2">
       <c r="D31" s="20"/>
       <c r="E31" s="20"/>
       <c r="F31" s="1"/>
       <c r="U31" s="12"/>
     </row>
-    <row r="32" spans="1:24" ns3:dyDescent="0.2">
+    <row r="32" spans="1:24" ns2:dyDescent="0.2">
       <c r="F32" s="1"/>
       <c r="U32" s="12"/>
     </row>
-    <row r="33" spans="6:21" ns3:dyDescent="0.2">
+    <row r="33" spans="6:21" ns2:dyDescent="0.2">
       <c r="F33" s="1"/>
       <c r="U33" s="12"/>
     </row>
-    <row r="34" spans="6:21" ns3:dyDescent="0.2">
+    <row r="34" spans="6:21" ns2:dyDescent="0.2">
       <c r="F34" s="1"/>
     </row>
-    <row r="35" spans="6:21" ns3:dyDescent="0.2">
+    <row r="35" spans="6:21" ns2:dyDescent="0.2">
       <c r="F35" s="1"/>
     </row>
-    <row r="36" spans="6:21" ns3:dyDescent="0.2">
+    <row r="36" spans="6:21" ns2:dyDescent="0.2">
       <c r="F36" s="1"/>
     </row>
-    <row r="37" spans="6:21" ns3:dyDescent="0.2">
+    <row r="37" spans="6:21" ns2:dyDescent="0.2">
       <c r="F37" s="1"/>
     </row>
-    <row r="38" spans="6:21" ns3:dyDescent="0.2">
+    <row r="38" spans="6:21" ns2:dyDescent="0.2">
       <c r="F38" s="1"/>
     </row>
-    <row r="39" spans="6:21" ns3:dyDescent="0.2">
+    <row r="39" spans="6:21" ns2:dyDescent="0.2">
       <c r="F39" s="1"/>
     </row>
-    <row r="40" spans="6:21" ns3:dyDescent="0.2">
+    <row r="40" spans="6:21" ns2:dyDescent="0.2">
       <c r="F40" s="1"/>
     </row>
-    <row r="41" spans="6:21" ns3:dyDescent="0.2">
+    <row r="41" spans="6:21" ns2:dyDescent="0.2">
       <c r="F41" s="1"/>
     </row>
-    <row r="42" spans="6:21" ns3:dyDescent="0.2">
+    <row r="42" spans="6:21" ns2:dyDescent="0.2">
       <c r="F42" s="1"/>
     </row>
-    <row r="43" spans="6:21" ns3:dyDescent="0.2">
+    <row r="43" spans="6:21" ns2:dyDescent="0.2">
       <c r="F43" s="1"/>
     </row>
-    <row r="44" spans="6:21" ns3:dyDescent="0.2">
+    <row r="44" spans="6:21" ns2:dyDescent="0.2">
       <c r="F44" s="1"/>
     </row>
-    <row r="45" spans="6:21" ns3:dyDescent="0.2">
+    <row r="45" spans="6:21" ns2:dyDescent="0.2">
       <c r="F45" s="1"/>
     </row>
-    <row r="46" spans="6:21" ns3:dyDescent="0.2">
+    <row r="46" spans="6:21" ns2:dyDescent="0.2">
       <c r="F46" s="1"/>
     </row>
-    <row r="47" spans="6:21" ns3:dyDescent="0.2">
+    <row r="47" spans="6:21" ns2:dyDescent="0.2">
       <c r="F47" s="1"/>
     </row>
-    <row r="48" spans="6:21" ns3:dyDescent="0.2">
+    <row r="48" spans="6:21" ns2:dyDescent="0.2">
       <c r="F48" s="1"/>
     </row>
-    <row r="49" spans="6:6" ns3:dyDescent="0.2">
+    <row r="49" spans="6:6" ns2:dyDescent="0.2">
       <c r="F49" s="1"/>
     </row>
-    <row r="50" spans="6:6" ns3:dyDescent="0.2">
+    <row r="50" spans="6:6" ns2:dyDescent="0.2">
       <c r="F50" s="1"/>
     </row>
-    <row r="51" spans="6:6" ns3:dyDescent="0.2">
+    <row r="51" spans="6:6" ns2:dyDescent="0.2">
       <c r="F51" s="1"/>
     </row>
-    <row r="52" spans="6:6" ns3:dyDescent="0.2">
+    <row r="52" spans="6:6" ns2:dyDescent="0.2">
       <c r="F52" s="1"/>
     </row>
-    <row r="53" spans="6:6" ns3:dyDescent="0.2">
+    <row r="53" spans="6:6" ns2:dyDescent="0.2">
       <c r="F53" s="1"/>
     </row>
-    <row r="54" spans="6:6" ns3:dyDescent="0.2">
+    <row r="54" spans="6:6" ns2:dyDescent="0.2">
       <c r="F54" s="1"/>
     </row>
-    <row r="55" spans="6:6" ns3:dyDescent="0.2">
+    <row r="55" spans="6:6" ns2:dyDescent="0.2">
       <c r="F55" s="1"/>
     </row>
-    <row r="56" spans="6:6" ns3:dyDescent="0.2">
+    <row r="56" spans="6:6" ns2:dyDescent="0.2">
       <c r="F56" s="1"/>
     </row>
-    <row r="57" spans="6:6" ns3:dyDescent="0.2">
+    <row r="57" spans="6:6" ns2:dyDescent="0.2">
       <c r="F57" s="1"/>
     </row>
-    <row r="58" spans="6:6" ns3:dyDescent="0.2">
+    <row r="58" spans="6:6" ns2:dyDescent="0.2">
       <c r="F58" s="1"/>
     </row>
-    <row r="59" spans="6:6" ns3:dyDescent="0.2">
+    <row r="59" spans="6:6" ns2:dyDescent="0.2">
       <c r="F59" s="1"/>
     </row>
-    <row r="60" spans="6:6" ns3:dyDescent="0.2">
+    <row r="60" spans="6:6" ns2:dyDescent="0.2">
       <c r="F60" s="1"/>
     </row>
-    <row r="61" spans="6:6" ns3:dyDescent="0.2">
+    <row r="61" spans="6:6" ns2:dyDescent="0.2">
       <c r="F61" s="1"/>
     </row>
-    <row r="62" spans="6:6" ns3:dyDescent="0.2">
+    <row r="62" spans="6:6" ns2:dyDescent="0.2">
       <c r="F62" s="1"/>
     </row>
-    <row r="63" spans="6:6" ns3:dyDescent="0.2">
+    <row r="63" spans="6:6" ns2:dyDescent="0.2">
       <c r="F63" s="1"/>
     </row>
-    <row r="64" spans="6:6" ns3:dyDescent="0.2">
+    <row r="64" spans="6:6" ns2:dyDescent="0.2">
       <c r="F64" s="1"/>
     </row>
-    <row r="65" spans="6:6" ns3:dyDescent="0.2">
+    <row r="65" spans="6:6" ns2:dyDescent="0.2">
       <c r="F65" s="1"/>
     </row>
-    <row r="66" spans="6:6" ns3:dyDescent="0.2">
+    <row r="66" spans="6:6" ns2:dyDescent="0.2">
       <c r="F66" s="1"/>
     </row>
-    <row r="67" spans="6:6" ns3:dyDescent="0.2">
+    <row r="67" spans="6:6" ns2:dyDescent="0.2">
       <c r="F67" s="1"/>
     </row>
-    <row r="68" spans="6:6" ns3:dyDescent="0.2">
+    <row r="68" spans="6:6" ns2:dyDescent="0.2">
       <c r="F68" s="1"/>
     </row>
-    <row r="69" spans="6:6" ns3:dyDescent="0.2">
+    <row r="69" spans="6:6" ns2:dyDescent="0.2">
       <c r="F69" s="1"/>
     </row>
-    <row r="70" spans="6:6" ns3:dyDescent="0.2">
+    <row r="70" spans="6:6" ns2:dyDescent="0.2">
       <c r="F70" s="1"/>
     </row>
-    <row r="71" spans="6:6" ns3:dyDescent="0.2">
+    <row r="71" spans="6:6" ns2:dyDescent="0.2">
       <c r="F71" s="1"/>
     </row>
-    <row r="72" spans="6:6" ns3:dyDescent="0.2">
+    <row r="72" spans="6:6" ns2:dyDescent="0.2">
       <c r="F72" s="1"/>
     </row>
-    <row r="73" spans="6:6" ns3:dyDescent="0.2">
+    <row r="73" spans="6:6" ns2:dyDescent="0.2">
       <c r="F73" s="1"/>
     </row>
-    <row r="74" spans="6:6" ns3:dyDescent="0.2">
+    <row r="74" spans="6:6" ns2:dyDescent="0.2">
       <c r="F74" s="1"/>
     </row>
-    <row r="75" spans="6:6" ns3:dyDescent="0.2">
+    <row r="75" spans="6:6" ns2:dyDescent="0.2">
       <c r="F75" s="1"/>
     </row>
-    <row r="76" spans="6:6" ns3:dyDescent="0.2">
+    <row r="76" spans="6:6" ns2:dyDescent="0.2">
       <c r="F76" s="1"/>
     </row>
-    <row r="77" spans="6:6" ns3:dyDescent="0.2">
+    <row r="77" spans="6:6" ns2:dyDescent="0.2">
       <c r="F77" s="1"/>
     </row>
-    <row r="78" spans="6:6" ns3:dyDescent="0.2">
+    <row r="78" spans="6:6" ns2:dyDescent="0.2">
       <c r="F78" s="1"/>
     </row>
-    <row r="79" spans="6:6" ns3:dyDescent="0.2">
+    <row r="79" spans="6:6" ns2:dyDescent="0.2">
       <c r="F79" s="1"/>
     </row>
-    <row r="80" spans="6:6" ns3:dyDescent="0.2">
+    <row r="80" spans="6:6" ns2:dyDescent="0.2">
       <c r="F80" s="1"/>
     </row>
-    <row r="81" spans="6:6" ns3:dyDescent="0.2">
+    <row r="81" spans="6:6" ns2:dyDescent="0.2">
       <c r="F81" s="1"/>
     </row>
-    <row r="82" spans="6:6" ns3:dyDescent="0.2">
+    <row r="82" spans="6:6" ns2:dyDescent="0.2">
       <c r="F82" s="1"/>
     </row>
-    <row r="83" spans="6:6" ns3:dyDescent="0.2">
+    <row r="83" spans="6:6" ns2:dyDescent="0.2">
       <c r="F83" s="1"/>
     </row>
-    <row r="84" spans="6:6" ns3:dyDescent="0.2">
+    <row r="84" spans="6:6" ns2:dyDescent="0.2">
       <c r="F84" s="1"/>
     </row>
-    <row r="85" spans="6:6" ns3:dyDescent="0.2">
+    <row r="85" spans="6:6" ns2:dyDescent="0.2">
       <c r="F85" s="1"/>
     </row>
-    <row r="86" spans="6:6" ns3:dyDescent="0.2">
+    <row r="86" spans="6:6" ns2:dyDescent="0.2">
       <c r="F86" s="1"/>
     </row>
-    <row r="87" spans="6:6" ns3:dyDescent="0.2">
+    <row r="87" spans="6:6" ns2:dyDescent="0.2">
       <c r="F87" s="1"/>
     </row>
-    <row r="88" spans="6:6" ns3:dyDescent="0.2">
+    <row r="88" spans="6:6" ns2:dyDescent="0.2">
       <c r="F88" s="1"/>
     </row>
-    <row r="89" spans="6:6" ns3:dyDescent="0.2">
+    <row r="89" spans="6:6" ns2:dyDescent="0.2">
       <c r="F89" s="1"/>
     </row>
-    <row r="90" spans="6:6" ns3:dyDescent="0.2">
+    <row r="90" spans="6:6" ns2:dyDescent="0.2">
       <c r="F90" s="1"/>
     </row>
-    <row r="91" spans="6:6" ns3:dyDescent="0.2">
+    <row r="91" spans="6:6" ns2:dyDescent="0.2">
       <c r="F91" s="1"/>
     </row>
-    <row r="92" spans="6:6" ns3:dyDescent="0.2">
+    <row r="92" spans="6:6" ns2:dyDescent="0.2">
       <c r="F92" s="1"/>
     </row>
-    <row r="93" spans="6:6" ns3:dyDescent="0.2">
+    <row r="93" spans="6:6" ns2:dyDescent="0.2">
       <c r="F93" s="1"/>
     </row>
-    <row r="94" spans="6:6" ns3:dyDescent="0.2">
+    <row r="94" spans="6:6" ns2:dyDescent="0.2">
       <c r="F94" s="1"/>
     </row>
-    <row r="95" spans="6:6" ns3:dyDescent="0.2">
+    <row r="95" spans="6:6" ns2:dyDescent="0.2">
       <c r="F95" s="1"/>
     </row>
-    <row r="96" spans="6:6" ns3:dyDescent="0.2">
+    <row r="96" spans="6:6" ns2:dyDescent="0.2">
       <c r="F96" s="1"/>
     </row>
-    <row r="97" spans="6:6" ns3:dyDescent="0.2">
+    <row r="97" spans="6:6" ns2:dyDescent="0.2">
       <c r="F97" s="1"/>
     </row>
-    <row r="98" spans="6:6" ns3:dyDescent="0.2">
+    <row r="98" spans="6:6" ns2:dyDescent="0.2">
       <c r="F98" s="1"/>
     </row>
-    <row r="99" spans="6:6" ns3:dyDescent="0.2">
+    <row r="99" spans="6:6" ns2:dyDescent="0.2">
       <c r="F99" s="1"/>
     </row>
-    <row r="100" spans="6:6" ns3:dyDescent="0.2">
+    <row r="100" spans="6:6" ns2:dyDescent="0.2">
       <c r="F100" s="1"/>
     </row>
-    <row r="101" spans="6:6" ns3:dyDescent="0.2">
+    <row r="101" spans="6:6" ns2:dyDescent="0.2">
       <c r="F101" s="1"/>
     </row>
-    <row r="102" spans="6:6" ns3:dyDescent="0.2">
+    <row r="102" spans="6:6" ns2:dyDescent="0.2">
       <c r="F102" s="1"/>
     </row>
-    <row r="103" spans="6:6" ns3:dyDescent="0.2">
+    <row r="103" spans="6:6" ns2:dyDescent="0.2">
       <c r="F103" s="1"/>
     </row>
-    <row r="104" spans="6:6" ns3:dyDescent="0.2">
+    <row r="104" spans="6:6" ns2:dyDescent="0.2">
       <c r="F104" s="1"/>
     </row>
-    <row r="105" spans="6:6" ns3:dyDescent="0.2">
+    <row r="105" spans="6:6" ns2:dyDescent="0.2">
       <c r="F105" s="1"/>
     </row>
-    <row r="106" spans="6:6" ns3:dyDescent="0.2">
+    <row r="106" spans="6:6" ns2:dyDescent="0.2">
       <c r="F106" s="1"/>
     </row>
-    <row r="107" spans="6:6" ns3:dyDescent="0.2">
+    <row r="107" spans="6:6" ns2:dyDescent="0.2">
       <c r="F107" s="1"/>
     </row>
-    <row r="108" spans="6:6" ns3:dyDescent="0.2">
+    <row r="108" spans="6:6" ns2:dyDescent="0.2">
       <c r="F108" s="1"/>
     </row>
-    <row r="109" spans="6:6" ns3:dyDescent="0.2">
+    <row r="109" spans="6:6" ns2:dyDescent="0.2">
       <c r="F109" s="1"/>
     </row>
-    <row r="110" spans="6:6" ns3:dyDescent="0.2">
+    <row r="110" spans="6:6" ns2:dyDescent="0.2">
       <c r="F110" s="1"/>
     </row>
-    <row r="111" spans="6:6" ns3:dyDescent="0.2">
+    <row r="111" spans="6:6" ns2:dyDescent="0.2">
       <c r="F111" s="1"/>
     </row>
-    <row r="112" spans="6:6" ns3:dyDescent="0.2">
+    <row r="112" spans="6:6" ns2:dyDescent="0.2">
       <c r="F112" s="1"/>
     </row>
-    <row r="113" spans="6:6" ns3:dyDescent="0.2">
+    <row r="113" spans="6:6" ns2:dyDescent="0.2">
       <c r="F113" s="1"/>
     </row>
-    <row r="114" spans="6:6" ns3:dyDescent="0.2">
+    <row r="114" spans="6:6" ns2:dyDescent="0.2">
       <c r="F114" s="1"/>
     </row>
-    <row r="115" spans="6:6" ns3:dyDescent="0.2">
+    <row r="115" spans="6:6" ns2:dyDescent="0.2">
       <c r="F115" s="1"/>
     </row>
-    <row r="116" spans="6:6" ns3:dyDescent="0.2">
+    <row r="116" spans="6:6" ns2:dyDescent="0.2">
       <c r="F116" s="1"/>
     </row>
-    <row r="117" spans="6:6" ns3:dyDescent="0.2">
+    <row r="117" spans="6:6" ns2:dyDescent="0.2">
       <c r="F117" s="1"/>
     </row>
-    <row r="118" spans="6:6" ns3:dyDescent="0.2">
+    <row r="118" spans="6:6" ns2:dyDescent="0.2">
       <c r="F118" s="1"/>
     </row>
-    <row r="119" spans="6:6" ns3:dyDescent="0.2">
+    <row r="119" spans="6:6" ns2:dyDescent="0.2">
       <c r="F119" s="1"/>
     </row>
-    <row r="120" spans="6:6" ns3:dyDescent="0.2">
+    <row r="120" spans="6:6" ns2:dyDescent="0.2">
       <c r="F120" s="1"/>
     </row>
-    <row r="121" spans="6:6" ns3:dyDescent="0.2">
+    <row r="121" spans="6:6" ns2:dyDescent="0.2">
       <c r="F121" s="1"/>
     </row>
-    <row r="122" spans="6:6" ns3:dyDescent="0.2">
+    <row r="122" spans="6:6" ns2:dyDescent="0.2">
       <c r="F122" s="1"/>
     </row>
-    <row r="123" spans="6:6" ns3:dyDescent="0.2">
+    <row r="123" spans="6:6" ns2:dyDescent="0.2">
       <c r="F123" s="1"/>
     </row>
-    <row r="124" spans="6:6" ns3:dyDescent="0.2">
+    <row r="124" spans="6:6" ns2:dyDescent="0.2">
       <c r="F124" s="1"/>
     </row>
-    <row r="125" spans="6:6" ns3:dyDescent="0.2">
+    <row r="125" spans="6:6" ns2:dyDescent="0.2">
       <c r="F125" s="1"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <mergeCells count="21">
-    <mergeCell ref="K4:V4"/>
+  <mergeCells count="29">
     <mergeCell ref="A17:B18"/>
     <mergeCell ref="C17:D18"/>
     <mergeCell ref="E17:E18"/>
     <mergeCell ref="L17:P18"/>
-    <mergeCell ref="K3:O3"/>
     <mergeCell ref="J17:K18"/>
     <mergeCell ref="A22:B23"/>
-    <mergeCell ref="K1:V1"/>
     <mergeCell ref="J19:K20"/>
     <mergeCell ref="T6:T7"/>
     <mergeCell ref="S6:S7"/>
@@ -2896,6 +4194,17 @@
     <mergeCell ref="Q22:R23"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E10:F10"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:V2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:V3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:V4"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:D8">
     <cfRule type="expression" dxfId="2" priority="7" stopIfTrue="1">
@@ -2913,24 +4222,21 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation showErrorMessage="1" sqref="K4 F23 C20 S18 S23 F20 C23 L20 S20 C17 L17 F18" ns2:uid="{00000000-0002-0000-0000-000000000000}"/>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="H10" ns2:uid="{00000000-0002-0000-0000-000001000000}"/>
-    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="H11:H13" ns2:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation showErrorMessage="1" sqref="K4 F23 C20 S18 S23 F20 C23 L20 S20 C17 L17 F18" ns1:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="H10" ns1:uid="{00000000-0002-0000-0000-000001000000}"/>
+    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="H11:H13" ns1:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I8" ns2:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I8" ns1:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="A3" ns4:id="rId1" display="www.federation.org" ns2:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="A4" ns4:id="rId2" display="records@federation.org" ns2:uid="{00000000-0004-0000-0000-000001000000}"/>
-  </hyperlinks>
+  <hyperlinks/>
   <pageMargins left="0.31496062992125984" right="0.35433070866141736" top="0.39370078740157483" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.31496062992125984"/>
-  <pageSetup paperSize="1" scale="70" firstPageNumber="0" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" ns4:id="rId3"/>
+  <pageSetup paperSize="1" scale="70" firstPageNumber="0" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" ns3:id="rId3"/>
   <headerFooter alignWithMargins="0"/>
-  <legacyDrawing ns4:id="rId4"/>
+  <legacyDrawing ns3:id="rId4"/>
 </worksheet>
 </file>